--- a/reports/jobs_2026-09-27.xlsx
+++ b/reports/jobs_2026-09-27.xlsx
@@ -3452,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3640,35 +3640,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Darwinbox</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://darwinbox.com/careers</t>
+          <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -3677,18 +3657,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3697,18 +3677,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3717,38 +3697,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://www.firstcry.com/careers</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>OYO</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://www.oyorooms.com/careers/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3757,58 +3717,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PharmEasy</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://pharmeasy.in/careers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pharmeasy.in/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pocket FM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://pocketfm.com/careers</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -3817,18 +3737,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -3837,18 +3757,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -3857,18 +3777,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>upGrad</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3877,18 +3797,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
